--- a/data/trans_dic/CAGE_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,73</t>
+          <t>0,49; 2,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,92</t>
+          <t>1,91; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,26</t>
+          <t>0,46; 3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,18</t>
+          <t>0,2; 2,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,19</t>
+          <t>0,23; 2,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,04</t>
+          <t>0,24; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 13,18</t>
+          <t>0,17; 12,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,8</t>
+          <t>0,48; 1,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,22</t>
+          <t>1,31; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,11</t>
+          <t>0,42; 1,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,26</t>
+          <t>0,12; 5,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,75</t>
+          <t>0,37; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,51</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,12</t>
+          <t>1,38; 4,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,96</t>
+          <t>1,01; 8,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,89</t>
+          <t>0,33; 1,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,33</t>
+          <t>0,29; 1,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,88</t>
+          <t>0,61; 1,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,58</t>
+          <t>1,04; 2,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,63</t>
+          <t>0,75; 5,29</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,7</t>
+          <t>0,28; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,25</t>
+          <t>1,12; 3,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,34</t>
+          <t>0,54; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,18</t>
+          <t>0,42; 3,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,29; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,94</t>
+          <t>0,21; 0,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,53</t>
+          <t>0,56; 1,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,33</t>
+          <t>0,35; 1,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,91</t>
+          <t>0,58; 2,62</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,81</t>
+          <t>1,0; 3,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,04</t>
+          <t>0,7; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,63</t>
+          <t>0,69; 3,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,38</t>
+          <t>0,17; 1,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,98</t>
+          <t>0,36; 3,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,9</t>
+          <t>0,52; 2,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,85</t>
+          <t>0,6; 1,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,92</t>
+          <t>0,75; 2,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,52</t>
+          <t>0,71; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,16</t>
+          <t>0,19; 3,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,5</t>
+          <t>0,71; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,43</t>
+          <t>2,69; 7,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,39</t>
+          <t>1,13; 5,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,12</t>
+          <t>0,45; 1,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,61</t>
+          <t>0,11; 1,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,34</t>
+          <t>0,58; 2,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,76</t>
+          <t>2,4; 5,64</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,96</t>
+          <t>0,33; 3,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,46</t>
+          <t>0,96; 4,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,08</t>
+          <t>0,15; 2,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,41</t>
+          <t>0,16; 2,38</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,19</t>
+          <t>0,69; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,89</t>
+          <t>0,77; 4,72</t>
         </is>
       </c>
     </row>
@@ -1697,27 +1697,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,19</t>
+          <t>0,52; 1,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,51</t>
+          <t>1,46; 2,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,94</t>
+          <t>1,06; 1,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,1</t>
+          <t>1,65; 3,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,52</t>
+          <t>0,13; 0,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,79</t>
+          <t>0,28; 0,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,23</t>
+          <t>0,56; 2,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,73</t>
+          <t>0,36; 0,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,79; 1,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,23</t>
+          <t>0,73; 1,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,47</t>
+          <t>1,26; 2,49</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2031; 13465</t>
+          <t>2414; 13277</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8169; 22338</t>
+          <t>8674; 23143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2282; 13691</t>
+          <t>1949; 12600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 869</t>
+          <t>0; 818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>950; 10199</t>
+          <t>935; 9610</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1025; 9422</t>
+          <t>1004; 9650</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>939; 8062</t>
+          <t>934; 8152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>173; 13063</t>
+          <t>169; 12080</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5171; 17272</t>
+          <t>4589; 17632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11660; 28439</t>
+          <t>11544; 27851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4133; 17207</t>
+          <t>3411; 15678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>474; 14151</t>
+          <t>316; 13963</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2722; 12892</t>
+          <t>2714; 13716</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8306; 24134</t>
+          <t>8166; 23411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7550; 24319</t>
+          <t>8134; 23675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2595; 18329</t>
+          <t>2333; 18490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 9632</t>
+          <t>0; 8703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1838; 10635</t>
+          <t>1842; 9777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3951; 18147</t>
+          <t>3905; 17199</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8010; 24352</t>
+          <t>7978; 22717</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11864; 29748</t>
+          <t>12055; 29734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3079; 17188</t>
+          <t>2787; 19600</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1786; 10844</t>
+          <t>1767; 10463</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7704; 22191</t>
+          <t>7623; 22901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3721; 15659</t>
+          <t>3626; 15796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1190; 8928</t>
+          <t>1180; 10528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>0; 4851</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6105</t>
+          <t>0; 6091</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 5599</t>
+          <t>440; 5527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2175; 12538</t>
+          <t>2766; 12782</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7297; 21334</t>
+          <t>7803; 22252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4753; 17725</t>
+          <t>4679; 17964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2638; 12562</t>
+          <t>2481; 11293</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2055</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5400; 23390</t>
+          <t>6141; 23680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4454; 19667</t>
+          <t>4492; 20420</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2249; 12353</t>
+          <t>2337; 12916</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5884</t>
+          <t>0; 5893</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2191</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1095; 8940</t>
+          <t>1101; 9222</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>660; 5585</t>
+          <t>672; 6262</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6929</t>
+          <t>0; 5872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6183; 23344</t>
+          <t>6347; 24922</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6929; 24015</t>
+          <t>7715; 23453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4259; 15395</t>
+          <t>3964; 15058</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2766; 13596</t>
+          <t>2759; 14603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>819; 13587</t>
+          <t>822; 13827</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3375; 16749</t>
+          <t>3386; 17169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6498; 19537</t>
+          <t>7080; 19500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6228</t>
+          <t>0; 5178</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 5048</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 10249</t>
+          <t>0; 10610</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1260; 7261</t>
+          <t>1521; 7582</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3630; 16727</t>
+          <t>3550; 15242</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1623; 14159</t>
+          <t>1005; 13595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5259; 22766</t>
+          <t>5618; 21025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9560; 22919</t>
+          <t>9554; 22421</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1847</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1034; 12271</t>
+          <t>1017; 12299</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5259</t>
+          <t>0; 5456</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1700; 8449</t>
+          <t>1813; 8207</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6387</t>
+          <t>0; 5430</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3457</t>
+          <t>0; 3546</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1021; 13825</t>
+          <t>1028; 13748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6217</t>
+          <t>0; 6912</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>738; 11268</t>
+          <t>730; 11119</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 5865</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 11143</t>
+          <t>0; 11787</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>572; 6196</t>
+          <t>694; 6317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>0; 2021</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5864</t>
+          <t>0; 5065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 11380</t>
+          <t>0; 10089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4582</t>
+          <t>0; 4572</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>964; 6186</t>
+          <t>971; 5973</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17045; 38902</t>
+          <t>17014; 38046</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50279; 85946</t>
+          <t>50005; 84334</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36392; 65896</t>
+          <t>36011; 65692</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24755; 48734</t>
+          <t>25905; 50138</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3720; 17659</t>
+          <t>4326; 18367</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1986; 11405</t>
+          <t>1989; 11445</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9745; 28031</t>
+          <t>9870; 27129</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5789; 22683</t>
+          <t>5657; 24072</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24809; 48344</t>
+          <t>24204; 47707</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55135; 91422</t>
+          <t>55382; 90084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>51351; 85316</t>
+          <t>50398; 83590</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>34586; 64109</t>
+          <t>32694; 64580</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/CAGE_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,69</t>
+          <t>0,54; 2,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,1</t>
+          <t>1,78; 5,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,0</t>
+          <t>0,49; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,06</t>
+          <t>0,2; 2,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,24</t>
+          <t>0,24; 2,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,19</t>
+          <t>1,52; 13,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,83</t>
+          <t>0,47; 1,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,15</t>
+          <t>1,25; 3,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,92</t>
+          <t>0,49; 2,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,19</t>
+          <t>0,79; 7,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,86</t>
+          <t>0,34; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,2; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,01</t>
+          <t>1,4; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,03</t>
+          <t>1,2; 7,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,73</t>
+          <t>0,33; 1,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,26</t>
+          <t>0,32; 1,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,75</t>
+          <t>0,68; 1,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,58</t>
+          <t>1,04; 2,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,29</t>
+          <t>0,88; 4,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,64</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,36</t>
+          <t>1,1; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,36</t>
+          <t>0,57; 2,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,74</t>
+          <t>0,72; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,68</t>
+          <t>0,27; 3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,6</t>
+          <t>0,52; 1,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,35</t>
+          <t>0,37; 1,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,62</t>
+          <t>0,74; 3,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,85</t>
+          <t>1,01; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,16</t>
+          <t>0,76; 2,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,8</t>
+          <t>0,84; 3,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,42</t>
+          <t>0,17; 1,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,34</t>
+          <t>0,34; 3,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,02</t>
+          <t>0,48; 1,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,81</t>
+          <t>0,56; 1,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,85</t>
+          <t>0,94; 3,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,78</t>
+          <t>0,74; 3,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,22</t>
+          <t>0,19; 3,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,59</t>
+          <t>0,72; 3,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,42</t>
+          <t>2,4; 6,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,63</t>
+          <t>1,12; 5,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,93</t>
+          <t>0,47; 2,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,55</t>
+          <t>0,2; 1,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,16</t>
+          <t>0,53; 2,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,64</t>
+          <t>2,21; 5,41</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,97</t>
+          <t>0,6; 4,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,34</t>
+          <t>0,95; 4,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,07</t>
+          <t>0,28; 1,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,38</t>
+          <t>0,87; 3,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,32</t>
+          <t>0,52; 5,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,72</t>
+          <t>0,7; 4,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,16</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,45; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,94</t>
+          <t>1,06; 1,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,19</t>
+          <t>1,78; 3,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,54</t>
+          <t>0,14; 0,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,32</t>
+          <t>0,06; 0,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,77</t>
+          <t>0,26; 0,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,37</t>
+          <t>1,09; 3,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,72</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,79; 1,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,2</t>
+          <t>0,74; 1,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,49</t>
+          <t>1,72; 2,89</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>7831</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2414; 13277</t>
+          <t>2661; 13846</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8674; 23143</t>
+          <t>8089; 23122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1949; 12600</t>
+          <t>2065; 13490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 818</t>
+          <t>0; 8771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>935; 9610</t>
+          <t>949; 9568</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1004; 9650</t>
+          <t>1013; 10520</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>934; 8152</t>
+          <t>938; 8149</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169; 12080</t>
+          <t>1687; 15358</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4589; 17632</t>
+          <t>4553; 17234</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11544; 27851</t>
+          <t>11098; 27602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3411; 15678</t>
+          <t>3962; 16987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>316; 13963</t>
+          <t>2186; 20157</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8857</t>
         </is>
       </c>
     </row>
@@ -2276,27 +2276,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2714; 13716</t>
+          <t>2531; 13619</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8166; 23411</t>
+          <t>8249; 23148</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8134; 23675</t>
+          <t>8295; 24147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2333; 18490</t>
+          <t>3000; 18137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8703</t>
+          <t>0; 9702</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1842; 9777</t>
+          <t>1856; 10591</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 4271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3905; 17199</t>
+          <t>4323; 18166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7978; 22717</t>
+          <t>8765; 24751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12055; 29734</t>
+          <t>12045; 30637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2787; 19600</t>
+          <t>3521; 19125</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>7815</t>
         </is>
       </c>
     </row>
@@ -2484,27 +2484,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1767; 10463</t>
+          <t>1925; 11565</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7623; 22901</t>
+          <t>7479; 22145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3626; 15796</t>
+          <t>3821; 14794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1180; 10528</t>
+          <t>2242; 12606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4851</t>
+          <t>0; 5085</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6091</t>
+          <t>0; 5447</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>440; 5527</t>
+          <t>460; 5707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2766; 12782</t>
+          <t>2726; 12755</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7803; 22252</t>
+          <t>7276; 22351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4679; 17964</t>
+          <t>4922; 18237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2481; 11293</t>
+          <t>3557; 15433</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9729</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6141; 23680</t>
+          <t>6203; 24583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4492; 20420</t>
+          <t>4884; 18823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2337; 12916</t>
+          <t>2943; 13461</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 6690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2722,32 +2722,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1101; 9222</t>
+          <t>1101; 9923</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>672; 6262</t>
+          <t>711; 6434</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5872</t>
+          <t>0; 5869</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6347; 24922</t>
+          <t>5966; 23530</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7715; 23453</t>
+          <t>7312; 25324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3964; 15058</t>
+          <t>5222; 17298</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15414</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2759; 14603</t>
+          <t>2846; 14429</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>822; 13827</t>
+          <t>815; 13223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3386; 17169</t>
+          <t>3422; 17390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7080; 19500</t>
+          <t>6709; 18951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5178</t>
+          <t>0; 5458</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5005</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 10610</t>
+          <t>0; 10709</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1521; 7582</t>
+          <t>1661; 7837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3550; 15242</t>
+          <t>3744; 16387</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1005; 13595</t>
+          <t>1781; 13862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5618; 21025</t>
+          <t>5203; 20203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9554; 22421</t>
+          <t>9451; 23109</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>5333</t>
         </is>
       </c>
     </row>
@@ -3113,17 +3113,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1017; 12299</t>
+          <t>1871; 13100</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5456</t>
+          <t>0; 4826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1813; 8207</t>
+          <t>1964; 9462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 1895</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1028; 13748</t>
+          <t>1877; 13002</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6912</t>
+          <t>0; 7146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>730; 11119</t>
+          <t>2500; 10380</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2879</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3316,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5865</t>
+          <t>0; 5084</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 11787</t>
+          <t>0; 11114</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4592</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>694; 6317</t>
+          <t>568; 5850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,27 +3351,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>0; 2245</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 10089</t>
+          <t>0; 11376</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4572</t>
+          <t>0; 5287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>971; 5973</t>
+          <t>980; 6711</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17014; 38046</t>
+          <t>16852; 37973</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50005; 84334</t>
+          <t>49698; 84873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36011; 65692</t>
+          <t>36001; 64060</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25905; 50138</t>
+          <t>29825; 55525</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4326; 18367</t>
+          <t>4632; 18511</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1989; 11445</t>
+          <t>1979; 12225</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9870; 27129</t>
+          <t>9260; 26200</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5657; 24072</t>
+          <t>9748; 28483</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24204; 47707</t>
+          <t>24974; 48973</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55382; 90084</t>
+          <t>55520; 90574</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50398; 83590</t>
+          <t>51207; 83935</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32694; 64580</t>
+          <t>44071; 74386</t>
         </is>
       </c>
     </row>
